--- a/data/S級DB_slim.xlsx
+++ b/data/S級DB_slim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7185" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8297" uniqueCount="812">
   <si>
     <t>開催日</t>
   </si>
@@ -2088,6 +2088,366 @@
   </si>
   <si>
     <t>犬伏湧也</t>
+  </si>
+  <si>
+    <t>取手</t>
+  </si>
+  <si>
+    <t>熊崎麻人</t>
+  </si>
+  <si>
+    <t>小川丈太</t>
+  </si>
+  <si>
+    <t>三浦貴大</t>
+  </si>
+  <si>
+    <t>大洞翔平</t>
+  </si>
+  <si>
+    <t>土屋裕二</t>
+  </si>
+  <si>
+    <t>竹内雄作</t>
+  </si>
+  <si>
+    <t>大塚玲</t>
+  </si>
+  <si>
+    <t>梁島邦友</t>
+  </si>
+  <si>
+    <t>坂田康季</t>
+  </si>
+  <si>
+    <t>松尾勇吾</t>
+  </si>
+  <si>
+    <t>渡辺十夢</t>
+  </si>
+  <si>
+    <t>清水剛志</t>
+  </si>
+  <si>
+    <t>原田翔真</t>
+  </si>
+  <si>
+    <t>小岩大介</t>
+  </si>
+  <si>
+    <t>中村隆生</t>
+  </si>
+  <si>
+    <t>望月湧世</t>
+  </si>
+  <si>
+    <t>平原啓多</t>
+  </si>
+  <si>
+    <t>林大悟</t>
+  </si>
+  <si>
+    <t>池田良</t>
+  </si>
+  <si>
+    <t>伊藤翔</t>
+  </si>
+  <si>
+    <t>久木原洋</t>
+  </si>
+  <si>
+    <t>佐伯翔</t>
+  </si>
+  <si>
+    <t>浮島知洋</t>
+  </si>
+  <si>
+    <t>田口勇介</t>
+  </si>
+  <si>
+    <t>冨久保雄介</t>
+  </si>
+  <si>
+    <t>石塚孝幸</t>
+  </si>
+  <si>
+    <t>安部貴之</t>
+  </si>
+  <si>
+    <t>邊見光輝</t>
+  </si>
+  <si>
+    <t>佐藤龍二</t>
+  </si>
+  <si>
+    <t>荒川達郎</t>
+  </si>
+  <si>
+    <t>南潤</t>
+  </si>
+  <si>
+    <t>加賀山淳</t>
+  </si>
+  <si>
+    <t>横山尚則</t>
+  </si>
+  <si>
+    <t>岩本和也</t>
+  </si>
+  <si>
+    <t>吉川嘉斗</t>
+  </si>
+  <si>
+    <t>柴崎淳</t>
+  </si>
+  <si>
+    <t>牧剛央</t>
+  </si>
+  <si>
+    <t>志村太賀</t>
+  </si>
+  <si>
+    <t>菊地圭尚</t>
+  </si>
+  <si>
+    <t>斎藤樂</t>
+  </si>
+  <si>
+    <t>大森慶一</t>
+  </si>
+  <si>
+    <t>山下一輝</t>
+  </si>
+  <si>
+    <t>太田龍希</t>
+  </si>
+  <si>
+    <t>中島将尊</t>
+  </si>
+  <si>
+    <t>内藤宣彦</t>
+  </si>
+  <si>
+    <t>植原琢也</t>
+  </si>
+  <si>
+    <t>長田龍拳</t>
+  </si>
+  <si>
+    <t>松尾信太郎</t>
+  </si>
+  <si>
+    <t>石川裕二</t>
+  </si>
+  <si>
+    <t>薦田将伍</t>
+  </si>
+  <si>
+    <t>根田空史</t>
+  </si>
+  <si>
+    <t>村上博幸</t>
+  </si>
+  <si>
+    <t>久米良</t>
+  </si>
+  <si>
+    <t>高橋築</t>
+  </si>
+  <si>
+    <t>川口聖二</t>
+  </si>
+  <si>
+    <t>治田知也</t>
+  </si>
+  <si>
+    <t>上田尭弥</t>
+  </si>
+  <si>
+    <t>瀬戸栄作</t>
+  </si>
+  <si>
+    <t>佐藤眞一</t>
+  </si>
+  <si>
+    <t>栗田貴徳</t>
+  </si>
+  <si>
+    <t>柿澤大貴</t>
+  </si>
+  <si>
+    <t>山根将太</t>
+  </si>
+  <si>
+    <t>長尾拳太</t>
+  </si>
+  <si>
+    <t>柴崎俊光</t>
+  </si>
+  <si>
+    <t>黒瀬浩太郎</t>
+  </si>
+  <si>
+    <t>藤根俊貴</t>
+  </si>
+  <si>
+    <t>黒沢征治</t>
+  </si>
+  <si>
+    <t>木村幸希</t>
+  </si>
+  <si>
+    <t>武藤篤弘</t>
+  </si>
+  <si>
+    <t>開坂秀明</t>
+  </si>
+  <si>
+    <t>神田龍</t>
+  </si>
+  <si>
+    <t>宿口潤平</t>
+  </si>
+  <si>
+    <t>川崎正安</t>
+  </si>
+  <si>
+    <t>湊聖二</t>
+  </si>
+  <si>
+    <t>丸山啓一</t>
+  </si>
+  <si>
+    <t>室井蓮太朗</t>
+  </si>
+  <si>
+    <t>吉田智哉</t>
+  </si>
+  <si>
+    <t>阪本和也</t>
+  </si>
+  <si>
+    <t>伊藤慶太郎</t>
+  </si>
+  <si>
+    <t>道場晃規</t>
+  </si>
+  <si>
+    <t>林慶次郎</t>
+  </si>
+  <si>
+    <t>松岡健介</t>
+  </si>
+  <si>
+    <t>池野健太</t>
+  </si>
+  <si>
+    <t>成清貴之</t>
+  </si>
+  <si>
+    <t>岡田亮太</t>
+  </si>
+  <si>
+    <t>藤田周健</t>
+  </si>
+  <si>
+    <t>菅原晃</t>
+  </si>
+  <si>
+    <t>坂本貴史</t>
+  </si>
+  <si>
+    <t>市橋司優人</t>
+  </si>
+  <si>
+    <t>志智俊夫</t>
+  </si>
+  <si>
+    <t>上田裕和</t>
+  </si>
+  <si>
+    <t>梅崎隆介</t>
+  </si>
+  <si>
+    <t>出澤拓也</t>
+  </si>
+  <si>
+    <t>比佐宝太</t>
+  </si>
+  <si>
+    <t>松尾透</t>
+  </si>
+  <si>
+    <t>杉本正隆</t>
+  </si>
+  <si>
+    <t>大石崇晴</t>
+  </si>
+  <si>
+    <t>誉田洋平</t>
+  </si>
+  <si>
+    <t>戸田洋平</t>
+  </si>
+  <si>
+    <t>小谷実</t>
+  </si>
+  <si>
+    <t>久田朔</t>
+  </si>
+  <si>
+    <t>脇本勇希</t>
+  </si>
+  <si>
+    <t>齊藤竜也</t>
+  </si>
+  <si>
+    <t>早坂秀悟</t>
+  </si>
+  <si>
+    <t>上原龍</t>
+  </si>
+  <si>
+    <t>山田駿武</t>
+  </si>
+  <si>
+    <t>中田雄喜</t>
+  </si>
+  <si>
+    <t>取鳥雄吾</t>
+  </si>
+  <si>
+    <t>佐々木堅次</t>
+  </si>
+  <si>
+    <t>松田治之</t>
+  </si>
+  <si>
+    <t>五日市誠</t>
+  </si>
+  <si>
+    <t>藤原誠</t>
+  </si>
+  <si>
+    <t>島田竜二</t>
+  </si>
+  <si>
+    <t>小倉竜二</t>
+  </si>
+  <si>
+    <t>武藤龍生</t>
+  </si>
+  <si>
+    <t>阿部将大</t>
+  </si>
+  <si>
+    <t>木村皆斗</t>
+  </si>
+  <si>
+    <t>守澤太志</t>
+  </si>
+  <si>
+    <t>長島大介</t>
   </si>
 </sst>
 </file>
@@ -52189,6 +52549,7755 @@
         <v>1.0</v>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C536" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D536" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E536" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F536" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G536" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H536" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I536" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J536" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K536" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L536" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M536" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C537" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D537" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E537" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F537" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G537" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H537" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I537" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J537" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K537" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L537" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M537" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C538" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D538" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E538" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F538" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G538" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H538" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I538" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J538" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K538" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L538" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M538" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C539" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D539" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E539" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F539" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G539" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H539" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I539" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J539" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K539" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L539" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M539" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C540" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D540" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E540" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="F540" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H540" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I540" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J540" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K540" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L540" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M540" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C541" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D541" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E541" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F541" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H541" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I541" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J541" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K541" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L541" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M541" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C542" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D542" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E542" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F542" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H542" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I542" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J542" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K542" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L542" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M542" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C543" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D543" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E543" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F543" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G543" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H543" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I543" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J543" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K543" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L543" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M543" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C544" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D544" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E544" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F544" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G544" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H544" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I544" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J544" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K544" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L544" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M544" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C545" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D545" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E545" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F545" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G545" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H545" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I545" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J545" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K545" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L545" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M545" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C546" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D546" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E546" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F546" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G546" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H546" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I546" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J546" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K546" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L546" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M546" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C547" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D547" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E547" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F547" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G547" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H547" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I547" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J547" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K547" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L547" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M547" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C548" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D548" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E548" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="F548" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G548" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H548" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I548" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J548" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K548" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L548" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M548" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C549" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D549" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E549" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="F549" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G549" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H549" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I549" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J549" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K549" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L549" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M549" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C550" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D550" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E550" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F550" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G550" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H550" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I550" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J550" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K550" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L550" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M550" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C551" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D551" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E551" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F551" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G551" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H551" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I551" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J551" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K551" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L551" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M551" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C552" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D552" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E552" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F552" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G552" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H552" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I552" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J552" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K552" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L552" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M552" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C553" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D553" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E553" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F553" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G553" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H553" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I553" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J553" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K553" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L553" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M553" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C554" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D554" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E554" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="F554" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G554" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H554" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I554" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J554" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K554" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L554" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M554" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C555" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D555" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E555" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F555" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G555" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H555" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I555" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J555" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K555" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L555" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M555" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C556" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D556" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E556" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F556" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G556" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H556" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I556" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J556" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K556" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L556" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M556" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C557" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D557" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E557" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F557" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G557" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H557" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I557" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J557" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L557" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M557" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C558" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D558" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E558" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F558" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G558" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H558" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I558" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J558" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K558" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L558" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M558" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C559" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D559" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E559" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="F559" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H559" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I559" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J559" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K559" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L559" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M559" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C560" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D560" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E560" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F560" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H560" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I560" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="J560" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K560" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L560" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M560" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C561" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D561" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F561" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H561" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I561" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J561" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K561" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L561" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M561" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C562" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D562" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E562" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="F562" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H562" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I562" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J562" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K562" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L562" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M562" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C563" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D563" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E563" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F563" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H563" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I563" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="J563" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K563" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L563" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M563" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C564" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D564" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E564" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F564" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G564" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H564" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I564" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J564" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K564" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L564" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M564" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C565" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D565" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F565" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G565" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H565" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I565" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J565" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K565" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L565" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M565" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C566" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D566" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E566" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F566" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G566" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H566" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I566" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J566" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K566" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L566" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M566" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C567" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D567" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E567" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F567" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G567" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H567" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I567" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J567" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K567" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L567" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M567" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C568" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D568" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F568" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G568" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H568" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I568" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J568" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K568" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L568" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M568" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C569" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D569" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F569" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G569" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H569" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I569" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J569" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K569" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L569" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M569" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C570" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D570" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E570" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="F570" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G570" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H570" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I570" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J570" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K570" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L570" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M570" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C571" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D571" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E571" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F571" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G571" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H571" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I571" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J571" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K571" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L571" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M571" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C572" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D572" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E572" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="F572" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G572" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H572" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I572" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="J572" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K572" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L572" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M572" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C573" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D573" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E573" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F573" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G573" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H573" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I573" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J573" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K573" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L573" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M573" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C574" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D574" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F574" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G574" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H574" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I574" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J574" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K574" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L574" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M574" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C575" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D575" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F575" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G575" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H575" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I575" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J575" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K575" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L575" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M575" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C576" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D576" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E576" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F576" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G576" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H576" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I576" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J576" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K576" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L576" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M576" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C577" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D577" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F577" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G577" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H577" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I577" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J577" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K577" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L577" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M577" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C578" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D578" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E578" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F578" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G578" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H578" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I578" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J578" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K578" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L578" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M578" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C579" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D579" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E579" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F579" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G579" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H579" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I579" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J579" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K579" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L579" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M579" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C580" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D580" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E580" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F580" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G580" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H580" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="I580" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J580" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K580" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L580" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M580" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C581" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D581" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E581" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F581" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G581" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H581" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I581" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J581" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K581" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L581" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M581" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C582" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D582" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F582" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G582" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H582" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I582" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J582" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K582" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L582" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M582" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C583" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D583" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E583" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F583" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G583" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H583" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I583" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="J583" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K583" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L583" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M583" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C584" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D584" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E584" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="F584" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G584" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H584" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I584" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J584" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K584" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L584" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M584" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C585" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D585" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E585" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F585" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G585" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H585" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I585" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J585" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K585" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L585" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M585" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C586" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D586" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F586" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G586" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H586" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I586" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J586" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K586" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L586" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M586" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C587" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D587" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E587" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F587" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G587" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H587" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I587" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J587" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K587" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L587" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M587" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C588" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D588" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F588" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G588" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H588" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="I588" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J588" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K588" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L588" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M588" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C589" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D589" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E589" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F589" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G589" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H589" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I589" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J589" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K589" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L589" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M589" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C590" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D590" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E590" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="F590" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G590" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H590" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I590" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J590" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K590" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L590" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M590" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C591" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D591" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="F591" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G591" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H591" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I591" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J591" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K591" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L591" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M591" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C592" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D592" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E592" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F592" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G592" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H592" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I592" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J592" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K592" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L592" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M592" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C593" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D593" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F593" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G593" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H593" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I593" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J593" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K593" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L593" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M593" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C594" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D594" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F594" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G594" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H594" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I594" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J594" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K594" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L594" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M594" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C595" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D595" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F595" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G595" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H595" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I595" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J595" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K595" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L595" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M595" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C596" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D596" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F596" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G596" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H596" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I596" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J596" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K596" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L596" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M596" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C597" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D597" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F597" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H597" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I597" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J597" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K597" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L597" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M597" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C598" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D598" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F598" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H598" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I598" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J598" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K598" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L598" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M598" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C599" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D599" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F599" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H599" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I599" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J599" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K599" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L599" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M599" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C600" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D600" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="F600" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G600" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H600" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I600" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J600" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K600" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L600" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M600" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C601" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D601" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="F601" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G601" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H601" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I601" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J601" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K601" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L601" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M601" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C602" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D602" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F602" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G602" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H602" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I602" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J602" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K602" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L602" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M602" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C603" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D603" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F603" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G603" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H603" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I603" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J603" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K603" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L603" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M603" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C604" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D604" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F604" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G604" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H604" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J604" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K604" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L604" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M604" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C605" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D605" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F605" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H605" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I605" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J605" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K605" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L605" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M605" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C606" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D606" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F606" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G606" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H606" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I606" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J606" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K606" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L606" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M606" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C607" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D607" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F607" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G607" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H607" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I607" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J607" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K607" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L607" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M607" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C608" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D608" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F608" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G608" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H608" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I608" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J608" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K608" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L608" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M608" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C609" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D609" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F609" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G609" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H609" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I609" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J609" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K609" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L609" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M609" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C610" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D610" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F610" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G610" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H610" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I610" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J610" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K610" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L610" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M610" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C611" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D611" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F611" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G611" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H611" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I611" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J611" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K611" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L611" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M611" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C612" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D612" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F612" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G612" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H612" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I612" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J612" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K612" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L612" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M612" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C613" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D613" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F613" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G613" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H613" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I613" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J613" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K613" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L613" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M613" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C614" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D614" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F614" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G614" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H614" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I614" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J614" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K614" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L614" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M614" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C615" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D615" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F615" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G615" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H615" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I615" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J615" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K615" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L615" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M615" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C616" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D616" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F616" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G616" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H616" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I616" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J616" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K616" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L616" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M616" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C617" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D617" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="F617" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H617" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I617" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J617" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K617" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L617" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M617" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C618" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D618" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F618" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G618" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H618" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I618" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J618" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K618" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L618" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M618" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C619" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D619" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F619" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G619" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H619" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I619" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J619" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K619" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L619" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M619" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C620" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D620" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F620" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G620" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H620" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I620" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J620" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K620" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L620" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M620" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C621" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D621" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F621" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G621" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H621" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I621" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J621" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K621" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L621" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M621" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C622" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D622" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F622" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G622" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H622" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I622" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J622" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K622" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L622" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M622" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C623" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D623" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F623" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G623" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H623" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I623" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J623" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K623" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L623" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M623" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C624" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D624" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F624" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G624" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H624" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I624" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J624" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K624" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L624" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M624" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C625" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D625" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F625" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G625" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H625" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I625" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J625" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K625" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L625" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M625" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C626" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D626" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F626" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G626" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H626" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I626" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J626" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K626" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L626" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M626" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C627" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D627" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F627" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G627" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H627" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I627" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J627" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K627" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L627" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M627" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C628" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D628" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F628" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G628" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H628" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I628" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J628" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K628" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L628" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M628" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C629" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D629" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F629" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G629" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H629" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I629" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J629" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K629" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L629" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M629" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C630" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D630" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F630" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G630" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H630" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I630" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J630" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K630" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L630" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M630" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C631" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D631" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F631" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G631" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H631" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I631" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J631" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K631" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L631" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M631" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C632" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D632" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F632" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G632" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H632" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I632" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J632" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K632" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L632" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M632" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C633" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D633" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F633" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G633" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H633" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I633" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J633" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K633" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L633" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M633" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C634" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D634" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F634" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G634" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H634" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I634" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J634" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K634" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L634" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M634" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C635" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D635" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F635" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G635" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H635" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I635" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J635" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K635" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L635" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M635" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C636" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D636" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F636" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G636" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H636" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I636" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J636" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K636" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L636" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M636" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C637" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D637" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F637" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G637" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H637" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I637" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J637" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K637" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L637" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M637" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C638" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D638" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F638" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G638" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H638" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I638" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J638" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K638" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L638" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M638" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C639" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D639" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F639" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G639" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H639" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I639" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J639" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K639" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L639" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M639" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C640" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D640" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F640" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G640" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H640" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I640" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J640" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K640" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L640" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M640" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C641" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D641" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F641" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G641" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H641" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I641" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J641" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K641" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L641" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M641" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C642" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D642" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F642" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G642" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H642" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I642" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J642" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K642" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L642" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M642" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C643" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D643" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F643" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G643" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H643" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I643" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J643" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K643" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L643" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M643" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C644" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D644" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F644" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G644" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H644" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I644" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J644" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K644" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L644" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M644" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C645" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D645" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F645" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G645" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H645" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I645" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J645" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K645" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L645" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M645" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C646" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D646" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F646" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G646" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H646" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I646" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J646" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K646" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L646" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M646" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C647" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D647" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F647" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G647" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H647" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I647" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J647" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K647" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L647" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M647" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C648" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D648" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F648" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G648" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H648" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I648" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J648" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K648" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L648" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M648" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C649" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D649" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F649" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G649" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H649" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I649" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J649" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K649" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L649" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M649" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C650" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D650" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F650" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G650" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H650" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I650" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J650" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K650" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L650" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M650" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C651" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D651" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F651" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G651" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H651" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I651" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J651" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K651" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L651" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M651" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C652" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D652" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F652" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G652" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H652" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I652" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J652" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K652" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L652" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M652" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C653" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D653" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F653" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G653" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H653" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I653" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J653" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K653" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L653" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M653" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C654" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D654" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F654" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G654" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H654" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I654" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J654" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K654" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L654" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M654" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C655" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D655" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F655" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G655" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H655" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I655" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J655" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K655" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L655" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M655" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C656" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D656" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F656" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G656" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H656" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I656" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J656" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K656" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L656" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M656" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C657" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D657" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F657" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G657" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I657" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J657" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K657" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L657" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M657" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C658" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D658" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F658" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G658" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H658" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I658" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J658" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K658" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L658" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M658" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C659" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D659" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F659" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G659" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H659" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I659" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J659" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K659" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L659" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M659" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C660" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D660" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="F660" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G660" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H660" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I660" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J660" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K660" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L660" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M660" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C661" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D661" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="F661" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G661" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H661" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I661" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J661" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K661" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L661" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M661" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C662" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D662" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F662" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G662" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H662" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I662" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J662" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K662" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L662" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M662" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C663" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D663" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F663" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G663" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H663" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I663" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J663" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K663" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L663" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M663" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C664" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D664" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F664" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G664" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H664" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I664" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J664" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K664" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L664" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M664" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C665" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D665" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F665" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G665" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H665" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I665" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J665" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K665" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L665" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M665" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C666" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D666" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F666" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G666" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H666" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I666" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J666" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K666" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L666" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M666" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C667" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D667" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F667" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G667" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H667" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I667" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J667" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K667" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L667" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M667" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C668" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D668" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F668" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G668" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H668" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I668" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J668" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K668" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L668" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M668" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C669" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D669" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F669" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G669" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H669" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I669" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J669" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K669" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L669" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M669" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C670" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D670" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F670" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G670" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H670" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I670" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J670" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K670" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L670" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M670" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C671" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D671" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="F671" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G671" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H671" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I671" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J671" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K671" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L671" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M671" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C672" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D672" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F672" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G672" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H672" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I672" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J672" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K672" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L672" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M672" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C673" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D673" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="F673" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G673" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H673" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I673" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J673" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K673" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L673" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M673" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C674" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D674" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F674" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G674" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H674" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I674" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J674" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K674" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L674" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M674" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C675" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D675" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="F675" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G675" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H675" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I675" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J675" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K675" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L675" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M675" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C676" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D676" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F676" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G676" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H676" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I676" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J676" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K676" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L676" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M676" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C677" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D677" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F677" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G677" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H677" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I677" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J677" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K677" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L677" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M677" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C678" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D678" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F678" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G678" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H678" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I678" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J678" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K678" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L678" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M678" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C679" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D679" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F679" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G679" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H679" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I679" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J679" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K679" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L679" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M679" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C680" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D680" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F680" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G680" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H680" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I680" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J680" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K680" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L680" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M680" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C681" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D681" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F681" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G681" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H681" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I681" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J681" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K681" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L681" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M681" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C682" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D682" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F682" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G682" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H682" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I682" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J682" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K682" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L682" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M682" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C683" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D683" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F683" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G683" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I683" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J683" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K683" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L683" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M683" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C684" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D684" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="F684" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G684" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H684" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I684" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J684" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K684" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L684" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M684" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C685" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D685" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F685" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G685" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H685" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I685" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J685" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K685" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L685" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M685" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C686" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D686" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F686" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G686" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H686" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I686" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J686" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K686" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L686" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M686" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C687" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D687" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="F687" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G687" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H687" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I687" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J687" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K687" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L687" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M687" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C688" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D688" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F688" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G688" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H688" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I688" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J688" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K688" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L688" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M688" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C689" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D689" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F689" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G689" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H689" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I689" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J689" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K689" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L689" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M689" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C690" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D690" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F690" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G690" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H690" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I690" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J690" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K690" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L690" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M690" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C691" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D691" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="F691" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G691" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H691" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I691" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J691" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K691" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L691" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M691" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C692" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D692" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F692" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G692" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H692" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I692" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J692" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K692" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L692" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M692" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C693" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D693" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F693" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G693" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H693" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I693" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J693" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K693" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L693" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M693" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C694" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D694" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="F694" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G694" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H694" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I694" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J694" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K694" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L694" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M694" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C695" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D695" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F695" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G695" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H695" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I695" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J695" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K695" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L695" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M695" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C696" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D696" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F696" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G696" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H696" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I696" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J696" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K696" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L696" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M696" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C697" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D697" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F697" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G697" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H697" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I697" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J697" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K697" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L697" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M697" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C698" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D698" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="F698" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G698" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H698" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I698" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J698" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K698" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L698" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M698" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C699" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D699" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F699" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G699" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H699" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="I699" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J699" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K699" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L699" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M699" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C700" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D700" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="F700" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H700" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I700" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J700" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K700" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L700" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M700" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C701" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D701" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="F701" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H701" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I701" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J701" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K701" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L701" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M701" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C702" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D702" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F702" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H702" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I702" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J702" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K702" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L702" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M702" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C703" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D703" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F703" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G703" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H703" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I703" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J703" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K703" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L703" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M703" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C704" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D704" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F704" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G704" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H704" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I704" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J704" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K704" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L704" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M704" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C705" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D705" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="F705" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G705" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H705" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I705" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J705" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K705" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L705" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M705" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C706" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D706" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="F706" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G706" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H706" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I706" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J706" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K706" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L706" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M706" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C707" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D707" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="F707" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G707" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H707" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I707" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J707" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K707" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L707" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M707" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C708" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D708" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="F708" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G708" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H708" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I708" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J708" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K708" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L708" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M708" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C709" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D709" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F709" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G709" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I709" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J709" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K709" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L709" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M709" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C710" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D710" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F710" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G710" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H710" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I710" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J710" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K710" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L710" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M710" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C711" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D711" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="F711" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G711" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H711" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I711" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J711" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K711" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L711" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M711" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C712" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D712" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="F712" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G712" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H712" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I712" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J712" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K712" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L712" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M712" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C713" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D713" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F713" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G713" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H713" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I713" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J713" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K713" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L713" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M713" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C714" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D714" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F714" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G714" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H714" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I714" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J714" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K714" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L714" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M714" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C715" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D715" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F715" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G715" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H715" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I715" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J715" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K715" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L715" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M715" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C716" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D716" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F716" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G716" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H716" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I716" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J716" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K716" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L716" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M716" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C717" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D717" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="F717" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G717" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H717" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I717" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J717" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K717" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L717" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M717" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C718" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D718" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F718" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G718" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H718" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="I718" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J718" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K718" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L718" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M718" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C719" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D719" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="F719" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G719" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H719" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I719" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J719" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K719" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L719" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M719" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C720" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D720" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F720" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G720" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H720" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I720" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J720" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K720" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L720" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M720" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C721" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D721" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="F721" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G721" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H721" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I721" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J721" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K721" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L721" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M721" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C722" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D722" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="F722" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G722" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H722" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I722" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J722" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K722" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L722" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M722" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C723" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D723" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="F723" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G723" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H723" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="I723" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J723" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K723" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L723" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M723" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2">
+        <v>46093.0</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C724" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D724" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F724" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G724" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H724" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I724" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="J724" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K724" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L724" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M724" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
